--- a/volumes/02-solar-home-systems/decision-tools/AEF_V2_D4_Receivables_Financing_Calculator.xlsx
+++ b/volumes/02-solar-home-systems/decision-tools/AEF_V2_D4_Receivables_Financing_Calculator.xlsx
@@ -724,7 +724,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AFRICA ENERGY FINANCE  |  VOLUME 2  |  SOLAR HOME SYSTEMS</t>
+          <t>AFRICA ENERGY FINANCE  |  BOOK 2  |  PAYGO SOLAR FINANCE</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -760,7 +760,7 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Decision tool D4  |  Version 1.0  |  Author &amp; ideation: Emmanuel Boujieka Kamga</t>
+          <t>Decision tool D4  |  Version 0.9 (pre-release)  |  Author &amp; ideation: Emmanuel Boujieka Kamga</t>
         </is>
       </c>
       <c r="B4" s="6" t="n"/>
@@ -852,7 +852,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1">
+    <row r="16" ht="30" customHeight="1">
       <c r="A16" s="9" t="inlineStr">
         <is>
           <t>Step 5</t>
@@ -860,7 +860,7 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>For a full plan with overheads, tax and interest, use the AEF SHS PAYGo model.</t>
+          <t>For a full plan with overheads, tax and interest, use MODEL 2, the PAYGo Company Financial and Investment Model.</t>
         </is>
       </c>
     </row>
@@ -905,7 +905,7 @@
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>Links to the Volume 2 model and book</t>
+          <t>Links to Book 2 and MODEL 2</t>
         </is>
       </c>
       <c r="B22" s="6" t="n"/>
@@ -977,7 +977,7 @@
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;L&amp;"Arial"&amp;8 Africa Energy Finance | Volume 2 Decision tool D4&amp;C&amp;"Arial"&amp;8 &amp;A&amp;R&amp;"Arial"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial"&amp;8 Africa Energy Finance | Book 2 Decision tool D4 | Version 0.9 (pre-release)&amp;C&amp;"Arial"&amp;8 &amp;A&amp;R&amp;"Arial"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1005,7 +1005,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AFRICA ENERGY FINANCE  |  VOLUME 2  |  SOLAR HOME SYSTEMS</t>
+          <t>AFRICA ENERGY FINANCE  |  BOOK 2  |  PAYGO SOLAR FINANCE</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1038,7 +1038,7 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Decision tool D4  |  Version 1.0  |  Author &amp; ideation: Emmanuel Boujieka Kamga</t>
+          <t>Decision tool D4  |  Version 0.9 (pre-release)  |  Author &amp; ideation: Emmanuel Boujieka Kamga</t>
         </is>
       </c>
       <c r="B4" s="6" t="n"/>
@@ -1287,7 +1287,7 @@
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;L&amp;"Arial"&amp;8 Africa Energy Finance | Volume 2 Decision tool D4&amp;C&amp;"Arial"&amp;8 &amp;A&amp;R&amp;"Arial"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial"&amp;8 Africa Energy Finance | Book 2 Decision tool D4 | Version 0.9 (pre-release)&amp;C&amp;"Arial"&amp;8 &amp;A&amp;R&amp;"Arial"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1315,7 +1315,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AFRICA ENERGY FINANCE  |  VOLUME 2  |  SOLAR HOME SYSTEMS</t>
+          <t>AFRICA ENERGY FINANCE  |  BOOK 2  |  PAYGO SOLAR FINANCE</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1348,7 +1348,7 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Decision tool D4  |  Version 1.0  |  Author &amp; ideation: Emmanuel Boujieka Kamga</t>
+          <t>Decision tool D4  |  Version 0.9 (pre-release)  |  Author &amp; ideation: Emmanuel Boujieka Kamga</t>
         </is>
       </c>
       <c r="B4" s="6" t="n"/>
@@ -2423,7 +2423,7 @@
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;L&amp;"Arial"&amp;8 Africa Energy Finance | Volume 2 Decision tool D4&amp;C&amp;"Arial"&amp;8 &amp;A&amp;R&amp;"Arial"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial"&amp;8 Africa Energy Finance | Book 2 Decision tool D4 | Version 0.9 (pre-release)&amp;C&amp;"Arial"&amp;8 &amp;A&amp;R&amp;"Arial"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -2508,7 +2508,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AFRICA ENERGY FINANCE  |  VOLUME 2  |  SOLAR HOME SYSTEMS</t>
+          <t>AFRICA ENERGY FINANCE  |  BOOK 2  |  PAYGO SOLAR FINANCE</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2712,7 +2712,7 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Decision tool D4  |  Version 1.0  |  Author &amp; ideation: Emmanuel Boujieka Kamga</t>
+          <t>Decision tool D4  |  Version 0.9 (pre-release)  |  Author &amp; ideation: Emmanuel Boujieka Kamga</t>
         </is>
       </c>
       <c r="B4" s="6" t="n"/>
@@ -18474,7 +18474,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;L&amp;"Arial"&amp;8 Africa Energy Finance | Volume 2 Decision tool D4&amp;C&amp;"Arial"&amp;8 &amp;A&amp;R&amp;"Arial"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial"&amp;8 Africa Energy Finance | Book 2 Decision tool D4 | Version 0.9 (pre-release)&amp;C&amp;"Arial"&amp;8 &amp;A&amp;R&amp;"Arial"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -18509,7 +18509,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AFRICA ENERGY FINANCE  |  VOLUME 2  |  SOLAR HOME SYSTEMS</t>
+          <t>AFRICA ENERGY FINANCE  |  BOOK 2  |  PAYGO SOLAR FINANCE</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -18563,7 +18563,7 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Decision tool D4  |  Version 1.0  |  Author &amp; ideation: Emmanuel Boujieka Kamga</t>
+          <t>Decision tool D4  |  Version 0.9 (pre-release)  |  Author &amp; ideation: Emmanuel Boujieka Kamga</t>
         </is>
       </c>
       <c r="B4" s="6" t="n"/>
@@ -21587,7 +21587,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;L&amp;"Arial"&amp;8 Africa Energy Finance | Volume 2 Decision tool D4&amp;C&amp;"Arial"&amp;8 &amp;A&amp;R&amp;"Arial"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial"&amp;8 Africa Energy Finance | Book 2 Decision tool D4 | Version 0.9 (pre-release)&amp;C&amp;"Arial"&amp;8 &amp;A&amp;R&amp;"Arial"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -21617,7 +21617,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AFRICA ENERGY FINANCE  |  VOLUME 2  |  SOLAR HOME SYSTEMS</t>
+          <t>AFRICA ENERGY FINANCE  |  BOOK 2  |  PAYGO SOLAR FINANCE</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -21656,7 +21656,7 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Decision tool D4  |  Version 1.0  |  Author &amp; ideation: Emmanuel Boujieka Kamga</t>
+          <t>Decision tool D4  |  Version 0.9 (pre-release)  |  Author &amp; ideation: Emmanuel Boujieka Kamga</t>
         </is>
       </c>
       <c r="B4" s="6" t="n"/>
@@ -21878,7 +21878,7 @@
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;L&amp;"Arial"&amp;8 Africa Energy Finance | Volume 2 Decision tool D4&amp;C&amp;"Arial"&amp;8 &amp;A&amp;R&amp;"Arial"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial"&amp;8 Africa Energy Finance | Book 2 Decision tool D4 | Version 0.9 (pre-release)&amp;C&amp;"Arial"&amp;8 &amp;A&amp;R&amp;"Arial"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -21908,7 +21908,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AFRICA ENERGY FINANCE  |  VOLUME 2  |  SOLAR HOME SYSTEMS</t>
+          <t>AFRICA ENERGY FINANCE  |  BOOK 2  |  PAYGO SOLAR FINANCE</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -21944,7 +21944,7 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Decision tool D4  |  Version 1.0  |  Author &amp; ideation: Emmanuel Boujieka Kamga</t>
+          <t>Decision tool D4  |  Version 0.9 (pre-release)  |  Author &amp; ideation: Emmanuel Boujieka Kamga</t>
         </is>
       </c>
       <c r="B4" s="6" t="n"/>
@@ -22076,7 +22076,7 @@
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;L&amp;"Arial"&amp;8 Africa Energy Finance | Volume 2 Decision tool D4&amp;C&amp;"Arial"&amp;8 &amp;A&amp;R&amp;"Arial"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial"&amp;8 Africa Energy Finance | Book 2 Decision tool D4 | Version 0.9 (pre-release)&amp;C&amp;"Arial"&amp;8 &amp;A&amp;R&amp;"Arial"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
